--- a/lucas/import_data/utility/observation/excel/provision_indicator.xlsx
+++ b/lucas/import_data/utility/observation/excel/provision_indicator.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="182">
   <si>
     <t xml:space="preserve">provision_id__provision_name</t>
   </si>
@@ -167,6 +167,18 @@
   </si>
   <si>
     <t xml:space="preserve">Aqua regia extraction P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture iuss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">derived</t>
+  </si>
+  <si>
+    <t xml:space="preserve">class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture usda</t>
   </si>
   <si>
     <t xml:space="preserve">lucas-wetlab-2015</t>
@@ -872,7 +884,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D1048576"/>
+  <dimension ref="A1:D144"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.65"/>
@@ -1205,41 +1217,41 @@
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C24" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>18</v>
@@ -1247,142 +1259,142 @@
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1390,13 +1402,13 @@
         <v>53</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1404,13 +1416,13 @@
         <v>53</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1418,13 +1430,13 @@
         <v>53</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1432,223 +1444,223 @@
         <v>53</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="C46" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="D50" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="D52" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="D53" s="1" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1656,13 +1668,13 @@
         <v>80</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="D56" s="1" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1670,13 +1682,13 @@
         <v>80</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1684,13 +1696,13 @@
         <v>80</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1698,122 +1710,122 @@
         <v>80</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="C61" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>7</v>
@@ -1821,13 +1833,13 @@
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>7</v>
@@ -1835,13 +1847,13 @@
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>7</v>
@@ -1849,13 +1861,13 @@
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>7</v>
@@ -1863,13 +1875,13 @@
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>7</v>
@@ -1877,13 +1889,13 @@
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>7</v>
@@ -1891,10 +1903,10 @@
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>108</v>
@@ -1905,10 +1917,10 @@
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>108</v>
@@ -1919,10 +1931,10 @@
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>108</v>
@@ -1933,13 +1945,13 @@
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>7</v>
@@ -1947,13 +1959,13 @@
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>7</v>
@@ -1961,13 +1973,13 @@
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>7</v>
@@ -1975,13 +1987,13 @@
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>7</v>
@@ -1989,13 +2001,13 @@
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>7</v>
@@ -2003,13 +2015,13 @@
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>7</v>
@@ -2017,181 +2029,181 @@
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="D82" s="1" t="s">
-        <v>122</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="D83" s="1" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>126</v>
+      <c r="D84" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>122</v>
+      <c r="D85" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>131</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="C93" s="1" t="s">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>7</v>
+        <v>136</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>11</v>
+        <v>125</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>7</v>
@@ -2199,21 +2211,21 @@
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="s">
-        <v>136</v>
+      <c r="A96" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>8</v>
@@ -2226,8 +2238,8 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="s">
-        <v>136</v>
+      <c r="A97" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>5</v>
@@ -2240,8 +2252,8 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="s">
-        <v>136</v>
+      <c r="A98" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>10</v>
@@ -2254,8 +2266,8 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="s">
-        <v>136</v>
+      <c r="A99" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>12</v>
@@ -2268,325 +2280,325 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
-        <v>137</v>
+      <c r="A100" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
-        <v>137</v>
+      <c r="A101" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>138</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
-        <v>137</v>
+      <c r="A102" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
-        <v>137</v>
+      <c r="A103" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>140</v>
+        <v>42</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>145</v>
+        <v>33</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>141</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>147</v>
+        <v>31</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>141</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>20</v>
+        <v>143</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>37</v>
+        <v>146</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>50</v>
+        <v>148</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>46</v>
+        <v>150</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>151</v>
+        <v>36</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>18</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="C114" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B115" s="1" t="s">
+      <c r="D117" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B116" s="1" t="s">
+      <c r="D119" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C120" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D116" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B117" s="1" t="s">
+      <c r="D120" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C121" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B118" s="1" t="s">
+      <c r="D121" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C122" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D118" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>161</v>
-      </c>
       <c r="D122" s="1" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2594,77 +2606,77 @@
         <v>158</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C124" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="B125" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>162</v>
+        <v>19</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>164</v>
+        <v>96</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>165</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>166</v>
@@ -2673,29 +2685,29 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>167</v>
+        <v>24</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>18</v>
@@ -2703,55 +2715,55 @@
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>162</v>
+        <v>26</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>18</v>
@@ -2759,55 +2771,55 @@
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>40</v>
+        <v>177</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>176</v>
+        <v>18</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>32</v>
+        <v>166</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>18</v>
@@ -2815,13 +2827,13 @@
     </row>
     <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>34</v>
+        <v>166</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>18</v>
@@ -2829,21 +2841,74 @@
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B140" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="C144" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D140" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="D144" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/lucas/import_data/utility/observation/excel/provision_indicator.xlsx
+++ b/lucas/import_data/utility/observation/excel/provision_indicator.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">transmittance spectroscopy</t>
   </si>
   <si>
-    <t xml:space="preserve">lucas-wetlab-2009</t>
+    <t xml:space="preserve">lucas wetlab 2009</t>
   </si>
   <si>
     <t xml:space="preserve">caco3</t>
@@ -178,7 +178,7 @@
     <t xml:space="preserve">soil texture usda</t>
   </si>
   <si>
-    <t xml:space="preserve">lucas-wetlab-2015</t>
+    <t xml:space="preserve">lucas wetlab 2015</t>
   </si>
   <si>
     <t xml:space="preserve">clay iso 13320:2009</t>
